--- a/batch4/projects/mldlnlp/Gen AI Project 1 Allocations.xlsx
+++ b/batch4/projects/mldlnlp/Gen AI Project 1 Allocations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d131965f25a4db2/Family-onedrive-vijay/Vijay/career/Engagements/Gynosis-Citius Tech/Batch 4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="8_{2B00F633-895C-4921-96EA-B2687CF73A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3651608E-980F-46F4-B770-50863A743FFD}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{2B00F633-895C-4921-96EA-B2687CF73A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{410C8387-C044-4FC6-BADC-7BF5FE2F1A37}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1410" windowWidth="18660" windowHeight="13960" xr2:uid="{B2840476-C673-4301-BF97-C4AA29BE5625}"/>
+    <workbookView xWindow="3040" yWindow="2040" windowWidth="18660" windowHeight="13960" xr2:uid="{B2840476-C673-4301-BF97-C4AA29BE5625}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Project</t>
   </si>
@@ -101,18 +101,6 @@
 Sai
 Vaishnavi
 </t>
-  </si>
-  <si>
-    <t>Shubham (rpa)</t>
-  </si>
-  <si>
-    <t>Sudarshan (rpa)</t>
-  </si>
-  <si>
-    <t>Prasanth (rpa)</t>
-  </si>
-  <si>
-    <t>Hetal (rpa)</t>
   </si>
   <si>
     <t xml:space="preserve">Manish
@@ -125,6 +113,25 @@
     <t>Mithila
 Shraddha
 Apoorva (non AI)</t>
+  </si>
+  <si>
+    <t>Group 6</t>
+  </si>
+  <si>
+    <t>Project 6:
+Semantic FAQ chatbot</t>
+  </si>
+  <si>
+    <t>Hetal (rpa)
+Shubham (rpa)
+Sudarshan (rpa)
+Prasanth (rpa)</t>
+  </si>
+  <si>
+    <t>THEME</t>
+  </si>
+  <si>
+    <t>ML, DL, NLP</t>
   </si>
 </sst>
 </file>
@@ -225,7 +232,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -566,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E45E9D79-C1A3-4E09-B68C-0B401F59ADE2}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" customWidth="1"/>
@@ -580,97 +587,112 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="8"/>
-    </row>
-    <row r="4" spans="1:4" ht="61" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="1:4" ht="61" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" ht="45.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:4" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C9" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C10" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C11" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C12" s="9" t="s">
-        <v>20</v>
-      </c>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C18" s="9"/>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C19" s="9"/>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C20" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
